--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXV/LTAIPT_A63F35C.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXV/LTAIPT_A63F35C.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="91">
   <si>
     <t>48998</t>
   </si>
@@ -158,31 +158,28 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2D0B36A741C7BB87D58075C535C874D6</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>5CF6C0BEE8F541D6FB6233477C48574F</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Subdirección Jurídica.</t>
-  </si>
-  <si>
-    <t>12/01/2023</t>
-  </si>
-  <si>
-    <t>10/01/2023</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no generó hipervínculo  por alguna recomendación por  organismos internacionales</t>
+    <t>Subdireción Jurídica</t>
+  </si>
+  <si>
+    <t>24/04/2023</t>
+  </si>
+  <si>
+    <t>Del periodo de 24 de enero del 2023 al 31 de marzo del 2023 el Colegio de Bachilleres del Estado de Tlaxcala no generó hipervínculo por alguna recomendación por organismos internacionales</t>
   </si>
   <si>
     <t>Comité contra las Desapariciones Forzadas</t>
@@ -689,7 +686,7 @@
   <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.140625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -705,7 +702,7 @@
     <col min="14" max="14" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="20" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="168.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="162.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
@@ -963,10 +960,10 @@
         <v>52</v>
       </c>
       <c r="P8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q8" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -980,7 +977,7 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I8:I200">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I8:I201">
       <formula1>Hidden_18</formula1>
     </dataValidation>
   </dataValidations>
@@ -995,187 +992,187 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
